--- a/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_003/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_vv40_cht_003/extracted.xlsx
@@ -485,6 +485,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -560,6 +565,21 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -630,11 +650,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="G4" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
     <comment ref="H4" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -740,12 +755,52 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="G7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="H7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
     <comment ref="I7" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="D8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="E8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="F8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="H8" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
+    <comment ref="I8" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1383,12 +1438,12 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Conjugate heat transfer model of aluminum serpentine cold plate for EV battery pack thermal management</t>
+          <t>Conjugate heat transfer model of aluminum serpentine cold plate for EV battery thermal management</t>
         </is>
       </c>
       <c r="C3" s="39" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 CHT model of a 50/50 EG-water cooled aluminum cold plate (AA6061-T6) dissipating 4.2 kW at steady state. The model supports a go/no-go decision for design-verification freeze on plate geometry and manifold sizing. Acceptance criteria: cell-to-cell temperature spread &lt;8°C and peak cell temperature &lt;48°C at 40°C ambient wind-off. Operating window: 0.6–1.0 kg/s, 30–50°C inlet, 3.5–5.0 kW heat load.</t>
+          <t>Ansys Fluent 2023 R2 CHT model of AA6061-T6 serpentine-channel cold plate with 50/50 EG-water coolant at 0.6–1.0 kg/s, 30–50°C inlet, 3.5–5.0 kW heat load. Used to support go/no-go decision for DV freeze on plate geometry and manifold sizing. Acceptance criteria: peak cell temperature &lt;48°C and cell-to-cell spread &lt;8°C at 40°C ambient wind-off.</t>
         </is>
       </c>
       <c r="D3" s="39" t="inlineStr">
@@ -1422,9 +1477,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="39" t="inlineStr">
+        <is>
+          <t>report.md</t>
         </is>
       </c>
       <c r="L3" s="40" t="inlineStr">
@@ -2020,7 +2075,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>Thermal Performance Acceptance Criterion</t>
+          <t>DV Freeze Thermal Performance Requirement</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
@@ -2030,7 +2085,7 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Peak cell temperature &lt;48°C and cell-to-cell spread &lt;8°C at 40°C ambient wind-off; pressure drop within acceptable range across 0.8–1.0 kg/s operating envelope</t>
+          <t>Peak cell temperature &lt;48°C and cell-to-cell spread &lt;8°C at 40°C ambient wind-off, 0.8–1.0 kg/s, 35°C inlet, 4.2 kW dissipation</t>
         </is>
       </c>
       <c r="E3" s="22" t="inlineStr">
@@ -2052,13 +2107,13 @@
       </c>
       <c r="B4" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 CHT Model</t>
+          <t>Ansys Fluent 2023 R2 CHT Cold Plate Model</t>
         </is>
       </c>
       <c r="C4" s="24" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Pressure-based coupled solver CHT model with poly-hexcore mesh, realizable k-ε turbulence, temperature-dependent NIST coolant properties, and UDFs for inlet ramp and heat map; three mesh refinement levels (5.6M, 11.9M, 24.7M cells)</t>
+          <t>Pressure-based coupled solver, realizable k-ε with enhanced wall treatment, poly-hexcore mesh (11.9M cells Medium), steady-state with pseudo-transient relaxation; includes UDF suite for inlet ramp, pump curve, and heat map</t>
         </is>
       </c>
       <c r="E4" s="33" t="n"/>
@@ -2072,13 +2127,13 @@
       </c>
       <c r="B5" s="41" t="inlineStr">
         <is>
-          <t>Bench Validation Test Data (Builds B2, B3)</t>
+          <t>Bench Validation Test Data (Builds B2 and B3)</t>
         </is>
       </c>
       <c r="C5" s="24" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Calorimeter loop measurements with Coriolis meter (±0.5%), 12 T-type thermocouples (±0.5°C), and FLIR A6750 IR camera at 0.8 and 1.0 kg/s flow rates with uniform and center-biased heat load profiles</t>
+          <t>Calorimeter-loop measurements at 0.8 and 1.0 kg/s with 12 T-type thermocouples (±0.5°C), FLIR A6750 IR camera, Coriolis flow meter (±0.5%); torque-controlled assembly at 2.0 N·m</t>
         </is>
       </c>
       <c r="E5" s="33" t="n"/>
@@ -2092,23 +2147,35 @@
       </c>
       <c r="B6" s="41" t="inlineStr">
         <is>
-          <t>UQ Sensitivity and Latin Hypercube Sample Set</t>
+          <t>TIM Compression and Thermal Property Data</t>
         </is>
       </c>
       <c r="C6" s="24" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Morris screening on 8 inputs and Latin hypercube sampling (N=60 executed of N=200 planned) reporting 95% interval on peak cell temperature of ±1.1°C at 1.0 kg/s; 500-sample reference in main deck inconsistent with archived run count</t>
+          <t>Lab compression tests on silicone TIM pad indicating correlation between pad thickness and measured effective conductivity; used (post-hoc) to adjust model TIM k from 3.0 to 2.6 W/m·K and thickness from 0.6 to 0.5 mm in Run V-07</t>
         </is>
       </c>
       <c r="E6" s="33" t="n"/>
       <c r="F6" s="33" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1" s="18">
-      <c r="A7" s="24" t="n"/>
-      <c r="B7" s="24" t="n"/>
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>Morris Screening and Latin Hypercube UQ Ensemble</t>
+        </is>
+      </c>
       <c r="C7" s="24" t="n"/>
-      <c r="D7" s="33" t="n"/>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Morris method on 8 inputs; LHS intended N=200, executed N=60 on Medium grid; 95% interval on peak cell temperature ±1.1°C at 1.0 kg/s; TIM k–thickness correlation not propagated</t>
+        </is>
+      </c>
       <c r="E7" s="33" t="n"/>
       <c r="F7" s="33" t="n"/>
     </row>
@@ -2248,7 +2315,7 @@
     <row r="3" ht="32.8" customHeight="1" s="18">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Steady-state temperature and pressure drop comparison at 0.8 kg/s</t>
+          <t>Bench comparison — 0.8 kg/s uniform heat load</t>
         </is>
       </c>
       <c r="B3" s="39" t="inlineStr">
@@ -2263,12 +2330,12 @@
       </c>
       <c r="D3" s="39" t="inlineStr">
         <is>
-          <t>Model compared to Build B2/B3 bench data at 0.8 kg/s, 35°C inlet, uniform 4.2 kW heat load. Peak cell delta T model vs. test: +2.3°C (model hotter); cell spread 6.9°C in both. Pressure drop mismatch 6–8%.</t>
+          <t>Model-to-test comparison of peak cell temperature and cell-to-cell spread at 0.8 kg/s, 35°C inlet, 4.2 kW uniform heat load using Build B3</t>
         </is>
       </c>
       <c r="E3" s="39" t="inlineStr">
         <is>
-          <t>B2/B3 calorimeter loop test data</t>
+          <t>12-thermocouple and IR measurements, Build B3</t>
         </is>
       </c>
       <c r="F3" s="39" t="inlineStr">
@@ -2283,7 +2350,7 @@
       </c>
       <c r="H3" s="39" t="inlineStr">
         <is>
-          <t>Peak ΔT error +2.3°C; pressure drop error 6–8%</t>
+          <t>Peak cell ΔT = +2.3°C (model hotter); spread 6.9°C in both model and test; pressure drop mismatch 6–8%</t>
         </is>
       </c>
       <c r="I3" s="42" t="inlineStr">
@@ -2295,7 +2362,7 @@
     <row r="4" ht="15" customHeight="1" s="18">
       <c r="A4" s="41" t="inlineStr">
         <is>
-          <t>Steady-state temperature and pressure drop comparison at 1.0 kg/s</t>
+          <t>Bench comparison — 1.0 kg/s uniform heat load</t>
         </is>
       </c>
       <c r="B4" s="41" t="inlineStr">
@@ -2306,27 +2373,23 @@
       <c r="C4" s="33" t="n"/>
       <c r="D4" s="41" t="inlineStr">
         <is>
-          <t>Model compared to Build B3 bench data at 1.0 kg/s, 35°C inlet, uniform heat load. Peak cell delta T: −0.4°C (model cooler); spread 7.1°C model vs. 8.0°C test; pressure drop within 3%. TIM conductivity and thickness were adjusted post-hoc prior to this comparison despite "no tuning" claim.</t>
+          <t>Model-to-test comparison of peak cell temperature and cell-to-cell spread at 1.0 kg/s, 35°C inlet, 4.2 kW uniform heat load using Build B3; TIM properties adjusted post-hoc prior to this run</t>
         </is>
       </c>
       <c r="E4" s="41" t="inlineStr">
         <is>
-          <t>B3 calorimeter loop test data</t>
+          <t>12-thermocouple and IR measurements, Build B3</t>
         </is>
       </c>
       <c r="F4" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G4" s="41" t="inlineStr">
-        <is>
-          <t>Latin hypercube (N=60); 95% interval ±1.1°C on peak cell temperature</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G4" s="33" t="n"/>
       <c r="H4" s="41" t="inlineStr">
         <is>
-          <t>Peak ΔT error −0.4°C; pressure drop error &lt;3%; UQ 95% CI ±1.1°C</t>
+          <t>Peak cell ΔT = −0.4°C; spread 7.1°C model vs. 8.0°C test; pressure drop within 3%</t>
         </is>
       </c>
       <c r="I4" s="42" t="inlineStr">
@@ -2338,7 +2401,7 @@
     <row r="5" ht="15" customHeight="1" s="18">
       <c r="A5" s="41" t="inlineStr">
         <is>
-          <t>Center-biased heat load IR hotspot comparison at 0.8 kg/s</t>
+          <t>Bench comparison — 0.8 kg/s center-biased heat load</t>
         </is>
       </c>
       <c r="B5" s="41" t="inlineStr">
@@ -2349,12 +2412,12 @@
       <c r="C5" s="33" t="n"/>
       <c r="D5" s="41" t="inlineStr">
         <is>
-          <t>Model IR hotspot prediction compared to FLIR A6750 measurement at 0.8 kg/s with +15% center-module heat map. Model under-predicts hotspot by 8%.</t>
+          <t>IR hotspot comparison at 0.8 kg/s with +15% center-module heat load pattern</t>
         </is>
       </c>
       <c r="E5" s="41" t="inlineStr">
         <is>
-          <t>FLIR A6750 IR thermal image data</t>
+          <t>FLIR A6750 IR camera, Build B3</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
@@ -2365,7 +2428,7 @@
       <c r="G5" s="33" t="n"/>
       <c r="H5" s="41" t="inlineStr">
         <is>
-          <t>IR hotspot error −8% (model under-predicts)</t>
+          <t>IR hotspot model −8% vs. test</t>
         </is>
       </c>
       <c r="I5" s="42" t="inlineStr">
@@ -2388,12 +2451,12 @@
       <c r="C6" s="33" t="n"/>
       <c r="D6" s="41" t="inlineStr">
         <is>
-          <t>Three-level mesh refinement (Coarse 5.6M, Medium 11.9M, Fine 24.7M cells). Medium-to-Fine peak cell temperature change 1.9°C; pressure drop change 1.8%. Coarse-to-Medium changes 2.3°C and 5.6% respectively. Fine grid used reduced prism layers (10 vs. 15) and shows y+ inconsistency (reported &lt;1.0 but post-processor overlay shows 3–7 at 1.0 kg/s).</t>
+          <t>Three-level poly-hexcore mesh refinement (Coarse 5.6M, Medium 11.9M, Fine 24.7M cells); peak cell temperature and pressure drop compared across levels; y+ consistency issue between Slides 5 and 6</t>
         </is>
       </c>
       <c r="E6" s="41" t="inlineStr">
         <is>
-          <t>Internal grid-to-grid comparison; no formal GCI computed</t>
+          <t>Internal grid-to-grid comparison; no GCI formally computed</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
@@ -2404,7 +2467,7 @@
       <c r="G6" s="33" t="n"/>
       <c r="H6" s="41" t="inlineStr">
         <is>
-          <t>Medium→Fine ΔT 1.9°C; Medium→Fine Δp 1.8%</t>
+          <t>Peak T Medium→Fine 1.9°C; Coarse→Medium 2.3°C; Δp Medium→Fine 1.8%; Fine grid used reduced prism layers (10 vs. 15)</t>
         </is>
       </c>
       <c r="I6" s="42" t="inlineStr">
@@ -2416,7 +2479,7 @@
     <row r="7" ht="15" customHeight="1" s="18">
       <c r="A7" s="41" t="inlineStr">
         <is>
-          <t>Code verification — manufactured source and energy balance checks</t>
+          <t>UQ sensitivity and uncertainty quantification</t>
         </is>
       </c>
       <c r="B7" s="41" t="inlineStr">
@@ -2427,40 +2490,73 @@
       <c r="C7" s="33" t="n"/>
       <c r="D7" s="41" t="inlineStr">
         <is>
-          <t>2D conduction manufactured-source test confirms source term sign conventions with L2 error &lt;0.2%. Closed-loop energy balance within 0.7% on Medium grid, 1.8% on Fine. Analytic laminar plate exchange comparison shows 2.5% deviation at Re~1500 (outside intended turbulent regime).</t>
+          <t>Morris method screening on 8 inputs followed by Latin hypercube sampling; executed N=60 of planned N=200; TIM k–thickness correlation not included; reported 95% CI on peak cell temperature</t>
         </is>
       </c>
       <c r="E7" s="41" t="inlineStr">
         <is>
-          <t>Analytical solutions; energy conservation check</t>
+          <t>Planned N=200 LHS; main deck erroneously cited N=500</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G7" s="41" t="inlineStr">
+        <is>
+          <t>Morris method (screening); Latin hypercube sampling (N=60)</t>
+        </is>
+      </c>
+      <c r="H7" s="41" t="inlineStr">
+        <is>
+          <t>95% interval on peak cell T at 1.0 kg/s: ±1.1°C; TIM thickness ranked top sensitivity input</t>
+        </is>
+      </c>
+      <c r="I7" s="42" t="inlineStr">
+        <is>
+          <t>Inconclusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="18">
+      <c r="A8" s="41" t="inlineStr">
+        <is>
+          <t>Code verification — manufactured source and energy balance</t>
+        </is>
+      </c>
+      <c r="B8" s="41" t="inlineStr">
+        <is>
+          <t>ValidationResult</t>
+        </is>
+      </c>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="41" t="inlineStr">
+        <is>
+          <t>2D manufactured-source test for conduction source term sign convention; closed-loop energy balance on Medium and Fine grids; analytic laminar plate comparison</t>
+        </is>
+      </c>
+      <c r="E8" s="41" t="inlineStr">
+        <is>
+          <t>Analytical solutions; energy conservation</t>
+        </is>
+      </c>
+      <c r="F8" s="41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G7" s="33" t="n"/>
-      <c r="H7" s="41" t="inlineStr">
-        <is>
-          <t>MMS L2 error &lt;0.2%; energy balance error 0.7% (Medium), 1.8% (Fine); analytic deviation 2.5%</t>
-        </is>
-      </c>
-      <c r="I7" s="42" t="inlineStr">
+      <c r="G8" s="33" t="n"/>
+      <c r="H8" s="41" t="inlineStr">
+        <is>
+          <t>MMS L2 error &lt;0.2%; energy balance 0.7% (Medium), 1.8% (Fine); analytic plate 2.5% at Re~1500</t>
+        </is>
+      </c>
+      <c r="I8" s="42" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="18">
-      <c r="A8" s="24" t="n"/>
-      <c r="B8" s="24" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="18">
       <c r="A9" s="24" t="n"/>
@@ -2667,12 +2763,12 @@
       </c>
       <c r="E5" s="42" t="inlineStr">
         <is>
-          <t>Commercially released solver with documented release notes; UDFs unit-tested; version control in place</t>
+          <t>Commercial solver with release-note review and UDF unit testing; known defects assessed</t>
         </is>
       </c>
       <c r="F5" s="41" t="inlineStr">
         <is>
-          <t>Ansys Fluent 2023 R2 with hotfix HF2; release notes reviewed; no known CHT coupling defects in R2 HF2. UDF suite (7 functions) has pytest unit tests at 94% line coverage. Perforce depot with hashed input decks and mesh files. One benign compiler warning unresolved and not independently reviewed. UDFs lack formal regression tests across Fluent point releases. One Fine run compiled with -O0 due to -O2 crash.</t>
+          <t>Ansys Fluent 2023 R2 with hotfix HF2 used; release notes and CHT coupling defects reviewed; UDF suite has 94% line coverage via pytest unit tests. Perforce configuration control with hashed input decks and meshes. Gaps: one benign compiler warning not independently reviewed; UDFs lack regression tests across Fluent point releases; one Fine-grid run compiled with -O0 due to -O2 crash (Slides 7, 12).</t>
         </is>
       </c>
       <c r="G5" s="41" t="inlineStr">
@@ -2700,12 +2796,12 @@
       </c>
       <c r="E6" s="42" t="inlineStr">
         <is>
-          <t>Comparison to analytical or manufactured solutions demonstrating correct equation implementation</t>
+          <t>Verification against analytical solutions or MMS for governing equations</t>
         </is>
       </c>
       <c r="F6" s="41" t="inlineStr">
         <is>
-          <t>2D conduction manufactured-source test confirms source term conventions with L2 error &lt;0.2%. Energy balance closed to 0.7% on Medium grid. Laminar analytic plate exchange comparison shows 2.5% deviation at Re~1500 (outside the turbulent operating regime so limited relevance). Checks are narrowly scoped but cover the key CHT coupling.</t>
+          <t>Manufactured-source test (2D conduction) confirms source term sign conventions with L2 error &lt;0.2%. Closed-loop energy balance within 0.7% on Medium grid. Laminar plate analytic comparison shows 2.5% deviation at Re~1500 (outside intended turbulent regime, noted as such). No full MMS for 3D turbulent CHT (Slide 7).</t>
         </is>
       </c>
       <c r="G6" s="41" t="inlineStr">
@@ -2733,12 +2829,12 @@
       </c>
       <c r="E7" s="42" t="inlineStr">
         <is>
-          <t>Formal mesh convergence with GCI or Richardson extrapolation; consistent y+ across refinement levels</t>
+          <t>Demonstrated mesh independence with quantified discretization error; consistent y+ across refinement levels</t>
         </is>
       </c>
       <c r="F7" s="41" t="inlineStr">
         <is>
-          <t>Three mesh levels studied; Medium→Fine peak temperature change 1.9°C and pressure drop change 1.8%. No formal GCI or Richardson extrapolation computed. Contradiction between claimed y+ &lt;1.0 on Medium and post-processor overlay showing y+ 3–7 at 1.0 kg/s on Fine. Fine grid used only 10 prism layers vs. 15 on coarser grids, undermining the refinement hierarchy. 0.6 kg/s case excluded from statistics due to sensor drift. Recommendation to re-run Fine with 15 prism layers remains open.</t>
+          <t>Three-level mesh study performed (5.6M/11.9M/24.7M cells). Medium→Fine peak T change 1.9°C and pressure drop 1.8% suggest approaching convergence but not fully achieved. No GCI or Richardson extrapolation computed. Critical inconsistency: Slide 5 claims average y+ &lt;1.0 on Medium but Slide 6 residual plots show y+ band 3–7 for 1.0 kg/s on Fine; Fine grid used only 10 prism layers vs. 15 on Medium due to memory limits, undermining refinement validity (Slides 5, 14).</t>
         </is>
       </c>
       <c r="G7" s="41" t="inlineStr">
@@ -2766,12 +2862,12 @@
       </c>
       <c r="E8" s="42" t="inlineStr">
         <is>
-          <t>All production runs converge to specified residual targets with monitored quantities flat</t>
+          <t>All production runs converge to defined residual and monitored-quantity targets</t>
         </is>
       </c>
       <c r="F8" s="41" t="inlineStr">
         <is>
-          <t>Standard convergence gates defined: energy to 1e-8, momentum to 1e-5, k/ε to 1e-5 with monitored outlet T and Δp flatness criteria. However, 0.6 kg/s case terminated at energy residual 3e-6 with ΔT still drifting 0.04°C/500 iterations. One Fine grid run accepted at ε residual 1e-4 due to UDF instability. One 0.8 kg/s Medium run used first-order upwind (oversight) yet results included in summary comparisons.</t>
+          <t>Residual targets defined (energy 1e-8, momentum 1e-5, k/ε 1e-5) with quantity monitors (ΔT &lt;0.01°C/500 iters, Δp &lt;2 Pa/500 iters). Exceptions documented: 0.6 kg/s run terminated at energy residual 3e-6 with ΔT still drifting 0.04°C/500 iters; one Fine-grid run accepted at ε residual 1e-4 after UDF instability; one Medium run used first-order upwind in a validation comparison (Slides 6, 9).</t>
         </is>
       </c>
       <c r="G8" s="41" t="inlineStr">
@@ -2799,12 +2895,12 @@
       </c>
       <c r="E9" s="42" t="inlineStr">
         <is>
-          <t>Independent review of boundary condition setup, mesh quality, and post-processing; consistent solver settings across all validation runs</t>
+          <t>Independent review of model setup, boundary conditions, and post-processing; consistent solver settings across all runs</t>
         </is>
       </c>
       <c r="F9" s="41" t="inlineStr">
         <is>
-          <t>Two design reviews held; mesh setup and post-processing scripts reviewed by a second analyst. However, test–model comparison package was compiled by the same engineer who owned the test rig (limited independence). Deprecated porous-jump fin approximation referenced in Slide 9 table. First-order upwind used inadvertently in one validation run. Two run logs missing due to Slurm outage. Compiler warning impact not independently assessed.</t>
+          <t>Mesh setup and post-processing scripts reviewed by a different analyst; two design reviews held. However, test–model comparison compiled by the same engineer who owned the test rig (limited separation). Deprecated porous-jump fin model still referenced in Slide 9 table. First-order upwind oversight in one validation run not caught before inclusion in summary (Slides 6, 9, 12).</t>
         </is>
       </c>
       <c r="G9" s="41" t="inlineStr">
@@ -2832,12 +2928,12 @@
       </c>
       <c r="E10" s="42" t="inlineStr">
         <is>
-          <t>Turbulence model selection justified for operating Re range; key physics included or absence justified</t>
+          <t>Physics model selection justified for the flow and heat transfer regime; known limitations documented</t>
         </is>
       </c>
       <c r="F10" s="41" t="inlineStr">
         <is>
-          <t>Realizable k-ε with enhanced wall treatment selected; Re_channel 9,000–12,000 justifies fully turbulent assumption (dimensionless group analysis on Slide 11). Thermal radiation disabled with IR data justification. Buoyancy, anisotropy, phase change, and ambient crossflow explicitly flagged as excluded with rationale. Uniform contact pressure assumption noted as a limitation. Transients, degradation, and manifold deformation deferred to future phases.</t>
+          <t>Realizable k-ε with enhanced wall treatment selected for Re_channel 9,000–12,000 (fully turbulent, Pe~3.6e5); justification via dimensionless group check on Slide 11. Radiation disabled with IR-data justification. Buoyancy via Boussinesq. Known limitations documented: no transients, no crossflow, no phase change, no TIM aging, no manifold deformation (Slides 3, 11, 13). Uniform contact pressure assumption noted as a simplification.</t>
         </is>
       </c>
       <c r="G10" s="41" t="inlineStr">
@@ -2865,12 +2961,12 @@
       </c>
       <c r="E11" s="42" t="inlineStr">
         <is>
-          <t>Material properties from traceable measurements; boundary conditions from calibrated instrumentation; input uncertainties characterized</t>
+          <t>Material properties from measurement or calibrated sources; boundary conditions matched to test measurements; input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="41" t="inlineStr">
         <is>
-          <t>NIST coolant polynomials used with viscosity clipping below 20°C. TIM conductivity adjusted from vendor 3.0 W/m·K to 2.6 W/m·K based on compression tests, but M7 lab note reveals further post-hoc reduction to ~2.6*(1-0.12) W/m·K and thickness changed from 0.6 mm to 0.5 mm in Run V-07 without disclosure in main text. Mass flow uncertainty ±2%; inlet temperature varied 34.5–35.5°C while model used fixed 35.0°C. TIM k and thickness correlation identified but not incorporated. Heat map assumed uniform in baseline; alternative pattern used in only one run.</t>
+          <t>Coolant properties from NIST polynomials with viscosity clipping below 20°C. TIM k adjusted from vendor 3.0 W/m·K to 2.6 W/m·K based on compression tests, but this adjustment was applied post-hoc to match IR data (contradiction with "no tuning" claim). TIM thickness changed to 0.5 mm in Run V-07 vs. BOM 0.6 mm. Flow rate uncertainty ±2%, inlet temperature uncertainty ±0.5°C characterized. Heat map assumed uniform in baseline; one center-bias variant tested (Slides 3, 8, 10).</t>
         </is>
       </c>
       <c r="G11" s="41" t="inlineStr">
@@ -2898,12 +2994,12 @@
       </c>
       <c r="E12" s="42" t="inlineStr">
         <is>
-          <t>Multiple production-representative builds; statistical characterization of sample variability</t>
+          <t>Multiple representative test articles; statistical characterization of sample-to-sample variation</t>
         </is>
       </c>
       <c r="F12" s="41" t="inlineStr">
         <is>
-          <t>Two physical builds (B2 without grease, B3 with thin grease) tested at standardized torque (2.0 N·m). Only two builds limits statistical characterization of manufacturing variability. Build-to-build TIM state differs (no grease vs. thin grease), complicating direct comparison. No sample size justification provided. IR emissivity calibration not independently replicated (camera available only one day).</t>
+          <t>Two builds tested: B2 (no grease) and B3 (thin grease with torque wrench 2.0 N·m). Only two builds provides minimal statistical characterization of assembly variability. No sample-size justification provided. Contact grease used only in B2 and B3 but configuration differences between builds not fully characterized in the comparison. TIM aging specimens not yet available (Slide 9, 13).</t>
         </is>
       </c>
       <c r="G12" s="41" t="inlineStr">
@@ -2931,12 +3027,12 @@
       </c>
       <c r="E13" s="42" t="inlineStr">
         <is>
-          <t>Calibrated instrumentation with documented uncertainty; controlled inlet conditions; traceable test standards</t>
+          <t>Calibrated instrumentation; controlled and measured test conditions; traceable to standards</t>
         </is>
       </c>
       <c r="F13" s="41" t="inlineStr">
         <is>
-          <t>Coriolis meter ±0.5%, 12 T-type thermocouples ±0.5°C, FLIR A6750 IR with emissivity 0.93. Inlet flow rate measured 0.78–1.02 kg/s with ±2% uncertainty; inlet temperature 34.5–35.5°C. Calorimeter loop configuration documented. Torque wrench used at 2.0 N·m. Emissivity assumption (0.93) not independently calibrated. No explicit reference to ASTM/ISO test standards.</t>
+          <t>Coriolis flow meter ±0.5%, 12 T-type thermocouples ±0.5°C, FLIR A6750 IR with emissivity 0.93 assumed. Torque wrench used at 2.0 N·m. Inlet temperature controlled 34.5–35.5°C during tests. Calorimeter loop used. Limitation: IR emissivity calibration not independently replicated; camera available only one day (Slides 9, 13).</t>
         </is>
       </c>
       <c r="G13" s="41" t="inlineStr">
@@ -2964,12 +3060,12 @@
       </c>
       <c r="E14" s="42" t="inlineStr">
         <is>
-          <t>Model boundary conditions set to match measured test conditions; input parameter differences quantified</t>
+          <t>Model boundary conditions demonstrably matched to measured test conditions; input parameter discrepancies quantified</t>
         </is>
       </c>
       <c r="F14" s="41" t="inlineStr">
         <is>
-          <t>Mass flow range 0.78–1.02 kg/s mapped to nominal 0.85 kg/s in model; inlet temperature fixed at 35.0°C vs. test range 34.5–35.5°C. Sensitivity of Δp to constant vs. temperature-dependent properties quantified (9%). However, TIM properties were altered between validation runs (V-05 to V-07) without transparent disclosure, undermining equivalency. Correlation between TIM k and thickness not propagated. Uniform heat assumption in baseline vs. actual module-level distribution not fully resolved.</t>
+          <t>Flow rate 0.78–1.02 kg/s in test; model used discrete nominal values. Inlet temperature 34.5–35.5°C in test; model used 35.0°C. Heat load uniform 4.2 kW in baseline; one center-bias variant. TIM properties in model not locked to independently measured values — post-hoc adjustment between V-05 and V-07 introduced before 1.0 kg/s comparison despite "no tuning" statement. Sensitivity of Δp to property choice confirmed (9% shift with constant properties). 0.6 kg/s profile excluded due to sensor drift (Slides 8, 9, 10).</t>
         </is>
       </c>
       <c r="G14" s="41" t="inlineStr">
@@ -2997,12 +3093,12 @@
       </c>
       <c r="E15" s="42" t="inlineStr">
         <is>
-          <t>Quantitative model-to-test error metrics at multiple operating points; uncertainty bands included in comparison</t>
+          <t>Quantitative model-to-test comparison at multiple operating points with uncertainty bands; consistent methodology across all comparison cases</t>
         </is>
       </c>
       <c r="F15" s="41" t="inlineStr">
         <is>
-          <t>Quantitative comparisons at two flow rates (0.8 and 1.0 kg/s): peak cell ΔT errors +2.3°C and −0.4°C respectively; spread criterion met in model at 1.0 kg/s but borderline in test (8.0°C). IR hotspot under-predicted by 8%. Pressure drop within 3% at 1.0 kg/s but 6–8% at 0.8 kg/s. UQ 95% CI ±1.1°C reported for 1.0 kg/s case only (N=60, underpowered vs. plan). Post-hoc TIM tuning not reflected transparently in comparison metrics. 0.6 kg/s point excluded. Inconsistent discretization order in one included validation run.</t>
+          <t>Quantitative comparisons at 0.8 and 1.0 kg/s for peak cell temperature and spread (ΔT +2.3°C and −0.4°C respectively) and pressure drop (within 3% at 1.0 kg/s; 6–8% at 0.8 kg/s). IR hotspot comparison at center-bias condition (−8%). However: one comparison case used first-order upwind (methodologically inconsistent); deprecated porous-jump model appears in one table; TIM properties adjusted between comparison runs; UQ interval ±1.1°C reported but from under-powered sample (N=60) and ignores k–t correlation (Slides 9, 10, 14).</t>
         </is>
       </c>
       <c r="G15" s="41" t="inlineStr">
@@ -3030,12 +3126,12 @@
       </c>
       <c r="E16" s="42" t="inlineStr">
         <is>
-          <t>QoIs directly address the acceptance criteria and are measurable both computationally and experimentally</t>
+          <t>QoIs directly address the acceptance criteria for DV freeze decision; measurable both in model and experiment</t>
         </is>
       </c>
       <c r="F16" s="41" t="inlineStr">
         <is>
-          <t>Peak cell temperature and cell-to-cell temperature spread directly correspond to the stated acceptance criteria (&lt;48°C peak, &lt;8°C spread). Both are computed by the model and measured by thermocouples and IR camera in the bench tests. Pressure drop is a secondary QoI relevant to pump sizing. Heat map bias sensitivity captures distribution effects. QoIs are well-defined and directly decision-relevant.</t>
+          <t>Peak cell temperature and cell-to-cell spread are the exact QoIs specified in the acceptance criteria (&lt;48°C peak, &lt;8°C spread) and are directly predicted by the CHT model and measured by thermocouples and IR camera in tests. Pressure drop is a secondary QoI relevant to manifold sizing. Both are extractable from model and test. QoI definition is clear and consistently applied across comparison slides (Slides 1, 9, 14).</t>
         </is>
       </c>
       <c r="G16" s="41" t="inlineStr">
@@ -3063,12 +3159,12 @@
       </c>
       <c r="E17" s="42" t="inlineStr">
         <is>
-          <t>Validation conditions span the claimed operating window; key COU physics regimes covered in test envelope</t>
+          <t>Validation conditions span the full COU operating envelope including boundary conditions, geometry, and physics regime</t>
         </is>
       </c>
       <c r="F17" s="41" t="inlineStr">
         <is>
-          <t>Validation covers 0.8 and 1.0 kg/s at 35°C inlet with uniform and center-biased heat loads, which partially spans the 0.6–1.0 kg/s, 30–50°C, 3.5–5.0 kW claimed COU. The 0.6 kg/s point was excluded due to sensor drift. Inlet temperature range 30–50°C is not exercised in validation (only 35°C tested). Transients &gt;60 s, ambient crossflow, dry-out, off-nominal glycol mix, TIM aging, and manifold deformation are all outside the test envelope and explicitly flagged. Stretch regions are identified but no uncertainty contribution for these gaps is quantified.</t>
+          <t>Validation performed at 0.8 and 1.0 kg/s, 35°C inlet, uniform heat load — within the COU envelope but not covering the full 0.6–1.0 kg/s, 30–50°C, 3.5–5.0 kW range. The 0.6 kg/s run was excluded due to sensor drift. Transients &gt;60 s, ambient crossflow, off-nominal glycol mix, and TIM aging are all outside the validated envelope and flagged as stretch regions. Center-bias heat distribution tested once. Validation geometry matches production CAD (Slides 2, 9, 13).</t>
         </is>
       </c>
       <c r="G17" s="41" t="inlineStr">
@@ -3157,7 +3253,7 @@
       </c>
       <c r="B3" s="39" t="inlineStr">
         <is>
-          <t>The model is accepted with conditions for DV freeze limited to 0.8–1.0 kg/s and 35–40°C inlet. At 1.0 kg/s the peak cell temperature prediction is within 0.4°C of Build B3 and pressure drop is within 3% of measurement, satisfying the primary acceptance criteria for that operating point. At 0.8 kg/s the peak cell error is larger (+2.3°C) and pressure drop mismatch is 6–8%, indicating reduced credibility at the lower bound of the freeze envelope. Required conditions before DV freeze executes: (1) re-run Fine grid with 15 prism layers and compute a formal GCI-like discretization error estimate to close the y+ inconsistency; (2) lock TIM thermal properties to independent compression and guarded-hot-plate measurements and rerun validation comparisons with transparent disclosure of any parameter changes; (3) execute at least 140 additional UQ samples (reaching N=200 as planned) or provide a statistical justification for N=60 sufficiency, and incorporate the identified TIM k–thickness correlation; (4) assign an independent reviewer to own the test–model comparison package. The 0.6 kg/s operating point and inlet temperatures outside 35–40°C are not covered by this acceptance. Transients, crossflow, TIM aging, and manifold deformation remain outside scope.</t>
+          <t>The model is accepted conditionally for a limited COU of 0.8–1.0 kg/s, 35–40°C inlet only. At 1.0 kg/s the peak cell temperature prediction is within 0.4°C of test and the spread criterion is met in the model; pressure drop is within 3%. These results are sufficient to support a DV freeze go decision within the stated envelope. However, the following conditions are imposed and must be resolved before extending the COU or relying on the model for margin analysis: (1) re-run the Fine grid with 15 prism layers and compute a formal GCI estimate to resolve the y+ inconsistency; (2) lock TIM thermal properties to independent compression/guarded-hot-plate measurements and rerun comparisons, removing the post-hoc adjustment; (3) execute at least 140 additional UQ samples (reaching the planned N=200) and incorporate the TIM k–thickness correlation; (4) assign an independent reviewer to own the test–model comparison package, separate from the test rig owner. The 0.6 kg/s, transient, crossflow, and off-nominal glycol regimes are explicitly outside the accepted COU. Risks of unaddressed items include potential underestimation of corner peak temperatures by ~2°C and spread exceeding 8°C under field torque variability.</t>
         </is>
       </c>
       <c r="C3" s="22" t="inlineStr">
